--- a/astro-site/public/dl/restaurant-schedule-templates/BONUS-02-restaurant-staffing-calculator.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/BONUS-02-restaurant-staffing-calculator.xlsx
@@ -206,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -334,6 +334,9 @@
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="13" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -873,7 +876,7 @@
     <row r="22">
       <c r="B22" s="19" t="inlineStr">
         <is>
-          <t>▸ It is not your payroll cost: it starts from one average salary and one employer payroll tax rate for the whole team. The real cost, contract by contract, comes from the "Payroll" tab of file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)) — a different workbook, not a tab of this one.</t>
+          <t>▸ It is not your payroll cost: it starts from one average salary and one employer payroll tax rate for the whole team. The real cost, contract by contract, comes from the "Payroll" tab of file 03 "Restaurant Labor Cost Calculator" — a different workbook, not a tab of this one.</t>
         </is>
       </c>
     </row>
@@ -1007,13 +1010,13 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="63" t="inlineStr">
         <is>
           <t>Average gross pay per pay period (team member, full-time):</t>
         </is>
       </c>
-      <c r="B9" s="63" t="n">
+      <c r="B9" s="64" t="n">
         <v>1400</v>
       </c>
     </row>
@@ -1037,8 +1040,8 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Paid hours per person per service (the full shift is these hours × the number of services):</t>
         </is>
@@ -1073,7 +1076,7 @@
           <t>Average check per cover, before sales tax:</t>
         </is>
       </c>
-      <c r="B15" s="64" t="n">
+      <c r="B15" s="65" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1359,7 +1362,7 @@
           <t>Estimated team labor cost (per month):</t>
         </is>
       </c>
-      <c r="B38" s="65">
+      <c r="B38" s="66">
         <f>IFERROR(IF(OR($B$29="",$B$9="",$B$10=""),"",ROUND($B$29*$B$9*$B$10/12*(1+$B$11),2)),"")</f>
         <v>23356.67</v>
       </c>
@@ -1370,7 +1373,7 @@
           <t>Estimated labor cost (per year):</t>
         </is>
       </c>
-      <c r="B39" s="65">
+      <c r="B39" s="66">
         <f>IF($B$38="","",ROUND($B$38*12,2))</f>
         <v>280280.04</v>
       </c>
@@ -1386,7 +1389,7 @@
           <t>Estimated sales for the month:</t>
         </is>
       </c>
-      <c r="B40" s="65">
+      <c r="B40" s="66">
         <f>IFERROR(IF(OR($B$5="",$B$15="",$B$7=""),"",ROUND($B$5*$B$15*$B$7*52/12,2)),"")</f>
         <v>72800.0</v>
       </c>
@@ -1477,14 +1480,14 @@
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="53" t="inlineStr">
         <is>
-          <t>▸ FTE = full-time people, not people per shift. And a PERSON-SERVICE is not a person: it is one person in ONE service. With the sample data that is 5 people per service and 2 services a day = 10 person-services, which are those SAME 5 people working an 8 h shift (4 paid hours per service × 2): 5 × 8 h × 6 days = 240 h a week = seven 40 h contracts with the 15% coverage for days off, vacation / PTO and sick leave already built in. It matches the "Shifts" tab of file 01 (Restaurant Schedule Template: Weekly &amp; Monthly Staff Rota): AM, PM and N are 8 h; the split is 9.</t>
+          <t>▸ FTE = full-time people, not people per shift. And a PERSON-SERVICE is not a person: it is one person in ONE service. With the sample data that is 5 people per service and 2 services a day = 10 person-services, which are those SAME 5 people working an 8 h shift (4 paid hours per service × 2): 5 × 8 h × 6 days = 240 h a week = seven 40 h contracts with the 15% coverage for days off, vacation / PTO and sick leave already built in. It matches the "Shifts" tab of file 01 "Restaurant Schedule Template": AM, PM and N are 8 h; the split is 9.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="53" t="inlineStr">
         <is>
-          <t>▸ The "Staffing Forecast" tab of file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)) does this same calculation and with the default values returns the same number. If you change the CONCEPT here, that tab does not find out: its three ratios are constants for Casual dining. Then copy B19, B20 and B21 of this calculator to B7, B8 and B9 of "Staffing Forecast" and they will match again.</t>
+          <t>▸ The "Staffing Forecast" tab of file 03 "Restaurant Labor Cost Calculator" does this same calculation and with the default values returns the same number. If you change the CONCEPT here, that tab does not find out: its three ratios are constants for Casual dining. Then copy B19, B20 and B21 of this calculator to B7, B8 and B9 of "Staffing Forecast" and they will match again.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1501,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="53" t="inlineStr">
         <is>
-          <t>▸ The cost is an estimate, not your payroll: it starts from one average gross pay and one employer payroll tax rate for the whole team. The real cost, contract by contract, comes from the "Payroll" tab of file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)).</t>
+          <t>▸ The cost is an estimate, not your payroll: it starts from one average gross pay and one employer payroll tax rate for the whole team. The real cost, contract by contract, comes from the "Payroll" tab of file 03 "Restaurant Labor Cost Calculator".</t>
         </is>
       </c>
     </row>
@@ -1545,21 +1548,21 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="11">
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Days open / week" prompt="It feeds the calculation through the weekly hours: opening 7 days instead of 6 raises the staff you need, not just the shift."/>
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Avg gross pay/period" prompt="This is the average GROSS PAY per pay period of a full-time employee, not their cost: employer payroll taxes &amp; insurance are added separately, two rows below. For the real cost of YOUR team use the &quot;Payroll&quot; tab of file 03 (Restaurant Labor Cost Calculator)."/>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Employer tax rate" prompt="Adjust to your state, insurer and unemployment rate. Estimate: about 10% = FICA 7.65% + FUTA/SUTA + workers' comp. UK: employer NI 15% above 5,000 a year + about 3% pension."/>
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Hours per service" prompt="The hours EACH person costs you per service, setup and close included. With 2 services a day, 4 h each make the 8 h shift of the &quot;Shifts&quot; tab of file 01. Raise it if services run long or you set up and close outside the shift."/>
-    <dataValidation sqref="B13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Contract hours/week" prompt="This is a full-time contract. Part-timers carry their own hours on their row: that is why the column is green and editable person by person."/>
-    <dataValidation sqref="B14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Coverage factor" prompt="An extra 15% on front-of-house (FOH) staff to cover days off, vacation / PTO and sick leave. In high season raise it to 1.20."/>
-    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · Avg check pre-tax" prompt="It is only used to check the result against your sales: without it the calculator can tell you to hire nineteen people without anything warning you that they eat up 100% of the till."/>
-    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="kitgp-v2c · PEAK-day covers" prompt="The busiest day of your week (Friday or Saturday, almost always). It drives the boost per service, which is what you add on that day, not for the whole week."/>
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid services per day" error="Pick 1, 2 or 3." promptTitle="kitgp-v2c · Invalid services/day" prompt="One (lunch only or dinner only), two (lunch and dinner) or three (breakfast, lunch and dinner). It splits the day's covers between services, and the service is what gets sized." type="list" errorStyle="stop">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Days open per week" prompt="It feeds the calculation through the weekly hours: opening 7 days instead of 6 raises the staff you need, not just the shift."/>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Avg gross pay per period" prompt="The average GROSS PAY per pay period of a full-time employee, not their cost: employer payroll taxes &amp; insurance are added two rows below. For the real cost of YOUR team use the &quot;Payroll&quot; tab of file 03 &quot;Restaurant Labor Cost Calculator&quot;."/>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Employer taxes &amp; insurance" prompt="Adjust to your state, insurer and unemployment rate. Estimate: about 10% = FICA 7.65% + FUTA/SUTA + workers' comp. UK: employer NI 15% above 5,000 a year + about 3% pension."/>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Hours per service" prompt="The hours EACH person costs you per service, setup and close included. With 2 services a day, 4 h each make the 8 h shift of the &quot;Shifts&quot; tab of file 01. Raise it if services run long or you set up and close outside the shift."/>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Full-time hours per week" prompt="Hours of a full-time contract (40 by default). Staff needed (FTE) = weekly hours needed ÷ these hours × the coverage factor."/>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Coverage factor" prompt="An extra 15% on top of the WHOLE team (kitchen, FOH and bar) to cover days off, vacation / PTO and sick leave. In high season raise it to 1.20."/>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Avg check before tax" prompt="It is only used to check the result against your sales: without it the calculator can tell you to hire nineteen people without anything warning you that they eat up 100% of the till."/>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Peak-day covers" prompt="The busiest day of your week (Friday or Saturday, almost always). It drives the boost per service, which is what you add on that day, not for the whole week."/>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid services per day" error="Pick 1, 2 or 3." promptTitle="Services per day" prompt="One (lunch only or dinner only), two (lunch and dinner) or three (breakfast, lunch and dinner). It splits the day's covers between services, and the service is what gets sized." type="list" errorStyle="stop">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid concept" error="Pick one of the ten concepts on the &quot;Ratios by Concept&quot; tab." promptTitle="kitgp-v2c · Invalid concept" prompt="The three ratios on &quot;Ratios by Concept&quot; and the two labor-cost traffic-light thresholds are looked up from here (VLOOKUP). The list holds exactly the ten concepts so that no other value can silently return the wrong ratios." type="list" errorStyle="stop">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid concept" error="Pick one of the ten concepts on the &quot;Ratios by Concept&quot; tab." promptTitle="Restaurant concept" prompt="The three ratios on &quot;Ratios by Concept&quot; and the two labor-cost traffic-light thresholds are looked up from here (VLOOKUP). The list holds exactly the ten concepts so that no other value can silently return the wrong ratios." type="list" errorStyle="stop">
       <formula1>"Casual dining,Fine dining,Fast casual / QSR,Café / brunch,Bar / cocktail bar,Pizzeria,Ghost kitchen / delivery,Hotel restaurant,Catering &amp; events,Ice cream shop / bakery"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid pay periods" error="Pick 52, 26, 24 or 12." promptTitle="kitgp-v2c · Invalid pay periods" prompt="52 = weekly, 26 = every two weeks (biweekly, the US norm), 24 = twice a month, 12 = monthly. The annual cost is driven by THIS cell, so it is never silently multiplied by a fixed number." type="list" errorStyle="stop">
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid pay periods" error="Pick 52, 26, 24 or 12." promptTitle="Pay periods per year" prompt="52 = weekly, 26 = every two weeks (biweekly, the US norm), 24 = twice a month, 12 = monthly. The annual cost is driven by THIS cell, so it is never silently multiplied by a fixed number." type="list" errorStyle="stop">
       <formula1>"52,26,24,12"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2129,7 +2132,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="53" t="inlineStr">
         <is>
-          <t>▸ "Target %" and "Acceptable %" are the same thresholds the traffic light in file 03 (Restaurant Labor Cost Calculator (Payroll &amp; Labor %)) uses for the six concepts that appear in both: the two files cannot contradict each other on the same ratio.</t>
+          <t>▸ "Target %" and "Acceptable %" are the same thresholds the traffic light in file 03 "Restaurant Labor Cost Calculator" uses for all ten concepts: the two files cannot contradict each other on the same ratio.</t>
         </is>
       </c>
     </row>
